--- a/data/8_docks.xlsx
+++ b/data/8_docks.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MetroSafe\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Me\UofL\Data Analytics &amp; System Optimization (DASO)\MetroSafe Drone-Project\MetroSafe-UofL_Drone_Optimization\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FACA353-A3EC-4F31-B332-8C45E1016636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BDD20B3-7BE0-4A34-945C-AEE4718B7600}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,30 +27,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
-    <t>1510 South 6th Street, Louisville, Kentucky 40208, United States</t>
-  </si>
-  <si>
-    <t>1525 Winter Avenue, Louisville, Kentucky 40204, United States</t>
-  </si>
-  <si>
-    <t>2620 Frankfort Avenue, Louisville, Kentucky 40206, United States</t>
-  </si>
-  <si>
-    <t>2900 Hikes Lane, Louisville, Kentucky 40218, United States</t>
-  </si>
-  <si>
-    <t>3228 River Park Drive, Louisville, Kentucky 40211, United States</t>
-  </si>
-  <si>
-    <t>3511 Fincastle Road, Louisville, Kentucky 40213, United States</t>
-  </si>
-  <si>
-    <t>4535 Manslick Road, Louisville, Kentucky 40216, United States</t>
-  </si>
-  <si>
-    <t>601 West Chestnut Street, Louisville, Kentucky 40203, United States</t>
-  </si>
-  <si>
     <t>Latitude</t>
   </si>
   <si>
@@ -58,6 +34,30 @@
   </si>
   <si>
     <t>Address</t>
+  </si>
+  <si>
+    <t>1510 South 6th Street</t>
+  </si>
+  <si>
+    <t>1525 Winter Avenue</t>
+  </si>
+  <si>
+    <t>2620 Frankfort Avenue</t>
+  </si>
+  <si>
+    <t>2900 Hikes Lane</t>
+  </si>
+  <si>
+    <t>3228 River Park Drive</t>
+  </si>
+  <si>
+    <t>3511 Fincastle Road</t>
+  </si>
+  <si>
+    <t>4535 Manslick Road</t>
+  </si>
+  <si>
+    <t>601 West Chestnut Street</t>
   </si>
 </sst>
 </file>
@@ -379,28 +379,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="61.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="61.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B2" s="1">
         <v>38.225943899999997</v>
@@ -409,9 +409,9 @@
         <v>-85.766279699999998</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B3" s="1">
         <v>38.237932700000002</v>
@@ -420,9 +420,9 @@
         <v>-85.723883799999996</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B4" s="1">
         <v>38.253996600000001</v>
@@ -431,9 +431,9 @@
         <v>-85.695403900000002</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B5" s="1">
         <v>38.209798200000002</v>
@@ -442,9 +442,9 @@
         <v>-85.642229999999998</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B6" s="1">
         <v>38.254015000000003</v>
@@ -453,9 +453,9 @@
         <v>-85.806982700000006</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B7" s="1">
         <v>38.207219600000002</v>
@@ -464,9 +464,9 @@
         <v>-85.715603299999998</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B8" s="1">
         <v>38.181624800000002</v>
@@ -475,9 +475,9 @@
         <v>-85.7985319</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B9" s="1">
         <v>38.249732799999997</v>
